--- a/Assets/Configs/Skills/三消肉鸽技能.xlsx
+++ b/Assets/Configs/Skills/三消肉鸽技能.xlsx
@@ -180,7 +180,7 @@
     <t>彩虹异变</t>
   </si>
   <si>
-    <t>彩球触发后，被消除的方块处有 15%/30%/50% 概率生成一个螺旋桨</t>
+    <t>彩球触发后，被消除的方块处有 5%/7%/10% 概率生成一个螺旋桨</t>
   </si>
   <si>
     <t>每个方块处的生成与否单独计算</t>
